--- a/knowledge-pack/copywriting/COPYWRITING_MASTER_MWTCB_REPAIRED.xlsx
+++ b/knowledge-pack/copywriting/COPYWRITING_MASTER_MWTCB_REPAIRED.xlsx
@@ -9,6 +9,7 @@
     <sheet name="RISK_VALIDATION" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="SOURCE_MAP" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="QA_REPORT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ContinuationSafeCopy" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -20,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -150,6 +151,9 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="33">
@@ -551,7 +555,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -559,6 +563,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0"/>
@@ -50777,4 +50782,103 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>part2_dialogue_6s_malay</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>part2_dialogue_8s_malay</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>part2_word_count</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>part2_lipsync_safe_flag</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>part2_cta_short</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>part2_no_vo_flag</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>part2_notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cap merah mudah cam waktu kelam-kabut. Tap beg kuning sekarang.</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Record word_count as 11 for this lane; kelam-kabut is treated as two spoken beats. No medical claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cap merah mudah cam waktu kelam-kabut, senang capai bila perlu. Tap beg kuning sekarang.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Google Flow 8s continuation stays household-standby only. No cure, guarantee, no-side-effects, or doctor-claim language.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>